--- a/source/AU/TD_AUv1.0.xlsx
+++ b/source/AU/TD_AUv1.0.xlsx
@@ -1,35 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1234414/Documents/Vocabularies/AU_Vocabularies/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84ECE6FA-642A-4247-B81A-6B17AFED6826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="33400" yWindow="9520" windowWidth="48700" windowHeight="15820" xr2:uid="{59A3A3E8-B1D5-7F44-83FF-EF45A3E1C521}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="observed variable" sheetId="1" r:id="rId1"/>
+    <sheet name="observed variable" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -38,1356 +22,1371 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="433">
   <si>
-    <t>organisation</t>
-  </si>
-  <si>
-    <t>scientist</t>
-  </si>
-  <si>
-    <t>trait name</t>
-  </si>
-  <si>
-    <t>trait description</t>
-  </si>
-  <si>
-    <t>trait alternative label</t>
-  </si>
-  <si>
-    <t>trait exactmatch</t>
-  </si>
-  <si>
-    <t>trait closematch</t>
-  </si>
-  <si>
-    <t>trait relatedmatch</t>
+    <t xml:space="preserve">organisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scientist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trait name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trait description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trait alternative label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trait exactmatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trait closematch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trait relatedmatch</t>
   </si>
   <si>
     <t xml:space="preserve">method name </t>
   </si>
   <si>
-    <t>method description</t>
-  </si>
-  <si>
-    <t>scale name</t>
-  </si>
-  <si>
-    <t>scale name alternative label</t>
-  </si>
-  <si>
-    <t>scale description</t>
-  </si>
-  <si>
-    <t>scale exactmatch</t>
-  </si>
-  <si>
-    <t>scale closematch</t>
-  </si>
-  <si>
-    <t>scale relatedmatch</t>
-  </si>
-  <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>Lou Haoyu</t>
-  </si>
-  <si>
-    <t>seed number</t>
+    <t xml:space="preserve">method description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale name alternative label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale exactmatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale closematch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale relatedmatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lou Haoyu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed number</t>
   </si>
   <si>
     <t xml:space="preserve">Total number of eligible seeds (i.e. seeds above a threshold size) for a plant </t>
   </si>
   <si>
-    <t>seedNum</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0000445; http://purl.obolibrary.org/obo/TO_0001134</t>
-  </si>
-  <si>
-    <t>seed number method</t>
-  </si>
-  <si>
-    <t>Scanning seed number (start from 1) using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>An integer is the number zero (0), a positive natural number (1, 2, 3, etc.) or a negative integer (−1, −2, −3, etc.)</t>
-  </si>
-  <si>
-    <t>seed blob size voxel</t>
-  </si>
-  <si>
-    <t>Size of the seed in voxel</t>
-  </si>
-  <si>
-    <t>blobsize</t>
-  </si>
-  <si>
-    <t>seed blob size voxel method</t>
-  </si>
-  <si>
-    <t>Scanning seed blob size in voxel using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed attenuation mean value</t>
-  </si>
-  <si>
-    <t>Mean attenuation value of this specific seed</t>
-  </si>
-  <si>
-    <t>attenuationmeanvalue</t>
-  </si>
-  <si>
-    <t>seed attenuation mean value method</t>
-  </si>
-  <si>
-    <t>Scanning seed attenuation mean value using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed spherical ratio</t>
-  </si>
-  <si>
-    <t>Describes the shape of the seed</t>
-  </si>
-  <si>
-    <t>sphericalratio</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/FLOPO_0002293</t>
-  </si>
-  <si>
-    <t>seed spherical ratio method</t>
-  </si>
-  <si>
-    <t>Scanning seed spherical ratio using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed spherical ratio scale 0-1</t>
-  </si>
-  <si>
-    <t>Seed spherical ratio scale. (0) Sphere shape; spherical ratio=0, infinitive long cylinder shape (seed shape), (1) Spherical ratio</t>
-  </si>
-  <si>
-    <t>seed spherical ratio spherical radius</t>
-  </si>
-  <si>
-    <t>Radius of a sphere that has the same volume as the seed</t>
-  </si>
-  <si>
-    <t>sphericalratiosphericalradius</t>
-  </si>
-  <si>
-    <t>seed spherical ratio spherical radius method</t>
-  </si>
-  <si>
-    <t>Scanning seed spherical ratio spherical radius using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed spherical ratio sphere minimum covering sphere radius</t>
-  </si>
-  <si>
-    <t>MCS=minimum covering sphere, radius of the smallest sphere surrounding the seed (SphericalRatioSphereRadius/SphericalRatioSphereMCSRadius=SphereicalRatio)</t>
-  </si>
-  <si>
-    <t>sphericalratiospheremcsradius</t>
-  </si>
-  <si>
-    <t>seed spherical ratio sphere minimum covering sphere radius method</t>
-  </si>
-  <si>
-    <t>Scanning seed spherical ratio sphere  minimum covering sphere radius using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed mean grey value</t>
-  </si>
-  <si>
-    <t>Mean grey value of the seed (corresponse to density)</t>
-  </si>
-  <si>
-    <t>meanvalue</t>
-  </si>
-  <si>
-    <t>seed mean grey value method</t>
+    <t xml:space="preserve">seedNum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0000445; http://purl.obolibrary.org/obo/TO_0001134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed number method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed number (start from 1) using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An integer is the number zero (0), a positive natural number (1, 2, 3, etc.) or a negative integer (−1, −2, −3, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed blob size voxel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size of the seed in voxel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blobsize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed blob size voxel method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed blob size in voxel using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed attenuation mean value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean attenuation value of this specific seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attenuationmeanvalue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed attenuation mean value method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed attenuation mean value using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed spherical ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Describes the shape of the seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sphericalratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/FLOPO_0002293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed spherical ratio method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed spherical ratio using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed spherical ratio scale 0-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seed spherical ratio scale. (0) Sphere shape; spherical ratio=0, infinitive long cylinder shape (seed shape), (1) Spherical ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed spherical ratio spherical radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radius of a sphere that has the same volume as the seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sphericalratiosphericalradius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed spherical ratio spherical radius method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed spherical ratio spherical radius using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed spherical ratio sphere minimum covering sphere radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCS=minimum covering sphere, radius of the smallest sphere surrounding the seed (SphericalRatioSphereRadius/SphericalRatioSphereMCSRadius=SphereicalRatio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sphericalratiospheremcsradius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed spherical ratio sphere minimum covering sphere radius method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed spherical ratio sphere  minimum covering sphere radius using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed mean grey value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean grey value of the seed (corresponse to density)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meanvalue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed mean grey value method</t>
   </si>
   <si>
     <t xml:space="preserve">Scanning seed mean grey  value using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. </t>
   </si>
   <si>
-    <t>seed center of mass X/Y/Z</t>
-  </si>
-  <si>
-    <t>Position of the center of mass of the seed within the volume in x/y/z (in pixel)</t>
-  </si>
-  <si>
-    <t>centerofmass_x/y/z</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/FLOPO_0015519</t>
-  </si>
-  <si>
-    <t>seed center of mass X/Y/Z method</t>
-  </si>
-  <si>
-    <t>Scanning seed center of mass X/Y/Z using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed minimum covering sphere radius</t>
-  </si>
-  <si>
-    <t>Minimum covering sphere</t>
-  </si>
-  <si>
-    <t>mcs_radius</t>
-  </si>
-  <si>
-    <t>seed minimum covering sphere radius method</t>
-  </si>
-  <si>
-    <t>Scanning seed minimum covering sphere radius using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed minimum covering sphere center X/Y/Z</t>
-  </si>
-  <si>
-    <t>Center position of the minimum covering sphere within the volume in x/y/z (in pixel)</t>
-  </si>
-  <si>
-    <t>mcs_center_X/Y/Z</t>
-  </si>
-  <si>
-    <t>seed minimum covering sphere center X/Y/Z method</t>
-  </si>
-  <si>
-    <t>Scanning seed minimum covering sphere center X/Y/Z using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed number of surface voxel</t>
-  </si>
-  <si>
-    <t>Number of voxels which firm the surface of the seed (seed surface area)</t>
-  </si>
-  <si>
-    <t>numberofsurfacevoxel</t>
-  </si>
-  <si>
-    <t>seed number of surface voxel method</t>
-  </si>
-  <si>
-    <t>Scanning seed number of surface voxel using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed blob size cubic millimeter</t>
-  </si>
-  <si>
-    <t>Size of the seed in cubic millimeter</t>
-  </si>
-  <si>
-    <t>blobsizecubicmillimeter</t>
-  </si>
-  <si>
-    <t>seed blob size cubic millimeter method</t>
-  </si>
-  <si>
-    <t>Scanning seed blob size cubic millimeter using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>cubic millimeter</t>
-  </si>
-  <si>
-    <t>mm3</t>
-  </si>
-  <si>
-    <t>A measure of volume in the metric system. One thousand ccs equal one liter</t>
-  </si>
-  <si>
-    <t>seed ratio surface to blob voxel</t>
-  </si>
-  <si>
-    <t>Ratio between the surface and the volume of the seed (surface area to volume ratio)</t>
-  </si>
-  <si>
-    <t>ratiosurfacetoblobvoxel</t>
-  </si>
-  <si>
-    <t>seed ratio surface to blob voxel method</t>
-  </si>
-  <si>
-    <t>Scanning seed ratio surface to blob voxel using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed length</t>
-  </si>
-  <si>
-    <t>Length of individual seeds</t>
-  </si>
-  <si>
-    <t>seedlength_mm</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0000146</t>
-  </si>
-  <si>
-    <t>seed length method</t>
-  </si>
-  <si>
-    <t>Scanning seed length using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>millimeter</t>
-  </si>
-  <si>
-    <t>mm</t>
-  </si>
-  <si>
-    <t>A length unit which is equal to one thousandth of a meter or 10^[-3] m</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0000016</t>
-  </si>
-  <si>
-    <t>seed estimated seed weight</t>
-  </si>
-  <si>
-    <t>Estimated seed weight derived from seed size and density measurement</t>
-  </si>
-  <si>
-    <t>estimatedseedweight</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0000181</t>
-  </si>
-  <si>
-    <t>seed estimated seed weight method</t>
-  </si>
-  <si>
-    <t>Estimated weight of the seed using X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>gram</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>A mass unit which is equal to one thousandth of a kilogram or 10^[-3] kg</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0000021</t>
-  </si>
-  <si>
-    <t>seed weight</t>
-  </si>
-  <si>
-    <t>Weight of the seed in grams (calculated by mass_correction_factor; mass_correction factor=mean value of actual weight/mean value of seed weight in g) (seed weight)</t>
-  </si>
-  <si>
-    <t>seedweight_g</t>
-  </si>
-  <si>
-    <t>seed weight method</t>
-  </si>
-  <si>
-    <t>Scanning weight of the seed in g (calculated by mass_correction_factor; mass_correction factor=mean value of actual weight/mean value of seed weight in g from the .csv) (seed weight) using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed surface area</t>
-  </si>
-  <si>
-    <t>Surface area of the seed</t>
-  </si>
-  <si>
-    <t>seedsurfacearea_mm2</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0002741</t>
-  </si>
-  <si>
-    <t>seed surface area method</t>
+    <t xml:space="preserve">seed center of mass X/Y/Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position of the center of mass of the seed within the volume in x/y/z (in pixel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">centerofmass_x/y/z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/FLOPO_0015519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed center of mass X/Y/Z method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed center of mass X/Y/Z using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed minimum covering sphere radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum covering sphere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcs_radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed minimum covering sphere radius method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed minimum covering sphere radius using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed minimum covering sphere center X/Y/Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center position of the minimum covering sphere within the volume in x/y/z (in pixel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcs_center_X/Y/Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed minimum covering sphere center X/Y/Z method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed minimum covering sphere center X/Y/Z using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed number of surface voxel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of voxels which firm the surface of the seed (seed surface area)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numberofsurfacevoxel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed number of surface voxel method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed number of surface voxel using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed blob size cubic millimeter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size of the seed in cubic millimeter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blobsizecubicmillimeter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed blob size cubic millimeter method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed blob size cubic millimeter using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cubic millimeter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A measure of volume in the metric system. One thousand ccs equal one liter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed ratio surface to blob voxel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio between the surface and the volume of the seed (surface area to volume ratio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ratiosurfacetoblobvoxel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed ratio surface to blob voxel method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed ratio surface to blob voxel using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Length of individual seeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedlength_mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0000146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed length method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed length using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">millimeter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A length unit which is equal to one thousandth of a meter or 10^[-3] m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/UO_0000016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed estimated seed weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated seed weight derived from seed size and density measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimatedseedweight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0000181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed estimated seed weight method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated weight of the seed using X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A mass unit which is equal to one thousandth of a kilogram or 10^[-3] kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/UO_0000021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight of the seed in grams (calculated by mass_correction_factor; mass_correction factor=mean value of actual weight/mean value of seed weight in g) (seed weight)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedweight_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed weight method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning weight of the seed in g (calculated by mass_correction_factor; mass_correction factor=mean value of actual weight/mean value of seed weight in g from the .csv) (seed weight) using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed surface area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface area of the seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedsurfacearea_mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0002741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed surface area method</t>
   </si>
   <si>
     <t xml:space="preserve">Scanning surface area of the seed using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. </t>
   </si>
   <si>
-    <t>square millimeter</t>
-  </si>
-  <si>
-    <t>mm2</t>
-  </si>
-  <si>
-    <t>An area unit which is equal to one millionth of a square meter or 10^[-6] m^[2]</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0000082</t>
-  </si>
-  <si>
-    <t>seed volume</t>
-  </si>
-  <si>
-    <t>Volume of the seed</t>
-  </si>
-  <si>
-    <t>seedvolume_mm3</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0007000</t>
-  </si>
-  <si>
-    <t>seed volume method</t>
-  </si>
-  <si>
-    <t>Scanning volume of the seed using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed structural similarity</t>
-  </si>
-  <si>
-    <t>Structural similarity of the seed.  0 - not similar to the seed class at all. 1 - identical with the seed class</t>
-  </si>
-  <si>
-    <t>ssim</t>
-  </si>
-  <si>
-    <t>seed structural similarity method</t>
-  </si>
-  <si>
-    <t>Scanning seed structural similarity using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
-  </si>
-  <si>
-    <t>seed structural similarity scale 0-1</t>
-  </si>
-  <si>
-    <t>Seed structural similarity scale. (0) not similar to the seed class at all, (1) identical with the seed class</t>
-  </si>
-  <si>
-    <t>seed class</t>
-  </si>
-  <si>
-    <t>Classification of the seed class 0=big, 1=medium, 2=small, 3=very small</t>
-  </si>
-  <si>
-    <t>seedclass</t>
-  </si>
-  <si>
-    <t>seed class method</t>
-  </si>
-  <si>
-    <t>Scanning seed class using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>seed class scale 0-3</t>
-  </si>
-  <si>
-    <t>Seed class scale. (0) Big, (1) medium, (2) small, (3) very small</t>
-  </si>
-  <si>
-    <t>spike seed number</t>
-  </si>
-  <si>
-    <t>Total number of seeds on this spike</t>
-  </si>
-  <si>
-    <t>seednumber</t>
-  </si>
-  <si>
-    <t>spike seed number method</t>
-  </si>
-  <si>
-    <t>Scanning spike sum of seed weight recorded in grams using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed weight total</t>
-  </si>
-  <si>
-    <t>Total weight of seeds</t>
-  </si>
-  <si>
-    <t>seedweight_total(g)</t>
-  </si>
-  <si>
-    <t>spike seed weight total method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed weight total using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment.</t>
-  </si>
-  <si>
-    <t>spike seed weight average</t>
-  </si>
-  <si>
-    <t>Average of seed weight on this spike</t>
-  </si>
-  <si>
-    <t>seedweight_ave(g)</t>
-  </si>
-  <si>
-    <t>spike seed weight average method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed weight average using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed weight standard deviation</t>
+    <t xml:space="preserve">square millimeter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An area unit which is equal to one millionth of a square meter or 10^[-6] m^[2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/UO_0000082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume of the seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedvolume_mm3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0007000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed volume method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning volume of the seed using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed structural similarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structural similarity of the seed.  0 - not similar to the seed class at all. 1 - identical with the seed class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed structural similarity method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed structural similarity using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed structural similarity scale 0-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seed structural similarity scale. (0) not similar to the seed class at all, (1) identical with the seed class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification of the seed class 0=big, 1=medium, 2=small, 3=very small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedclass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed class method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning seed class using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed class scale 0-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seed class scale. (0) Big, (1) medium, (2) small, (3) very small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of seeds on this spike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seednumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed number method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike sum of seed weight recorded in grams using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed weight total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total weight of seeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedweight_total(g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed weight total method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed weight total using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed weight average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average of seed weight on this spike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedweight_ave(g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed weight average method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed weight average using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed weight standard deviation</t>
   </si>
   <si>
     <t xml:space="preserve">Standard deviation of average seed weight </t>
   </si>
   <si>
-    <t>seedweight_avesd</t>
-  </si>
-  <si>
-    <t>spike seed weight standard deviation method</t>
-  </si>
-  <si>
-    <t>Scanning spike standard deviation of seed weight average using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed spherical ratio average</t>
-  </si>
-  <si>
-    <t>Average of shape descriptor of seed on spike</t>
-  </si>
-  <si>
-    <t>sphericalratio_ave</t>
-  </si>
-  <si>
-    <t>spike seed spherical ratio average method</t>
-  </si>
-  <si>
-    <t>Scanning spike spike seed spherical ratio average using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed spherical ratio average 0-1</t>
-  </si>
-  <si>
-    <t>Spike seed spherical ratio average scale 0 = infinitive long cylinder shape, 1 = sphere shape</t>
-  </si>
-  <si>
-    <t>spike seed length average</t>
-  </si>
-  <si>
-    <t>Average length of seeds on this spike</t>
-  </si>
-  <si>
-    <t>seedlength(mm)</t>
-  </si>
-  <si>
-    <t>spike seed length average method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed length using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed length standard deviation</t>
-  </si>
-  <si>
-    <t>Standard deviation of seed length (mm)</t>
-  </si>
-  <si>
-    <t>seedlength_sd</t>
-  </si>
-  <si>
-    <t>spike seed length standard deviation method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed length standard deviation using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed volume</t>
-  </si>
-  <si>
-    <t>Average seed volume in mm3</t>
-  </si>
-  <si>
-    <t>seedVolume_mm3</t>
-  </si>
-  <si>
-    <t>spike seed volume method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed volume using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed size</t>
-  </si>
-  <si>
-    <t>Averge seed size in mm3</t>
-  </si>
-  <si>
-    <t>seedsize(mm3)</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0000391</t>
-  </si>
-  <si>
-    <t>spike seed size method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed size using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed size standard deviation</t>
-  </si>
-  <si>
-    <t>Standard deviation of Seed size</t>
-  </si>
-  <si>
-    <t>seedsize_sd</t>
-  </si>
-  <si>
-    <t>spike seed size standard deviation method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed size standard deviation using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment.</t>
-  </si>
-  <si>
-    <t>spike seed surface area</t>
-  </si>
-  <si>
-    <t>Average seed surface area (mm2)</t>
-  </si>
-  <si>
-    <t>surfacearea(mm2)</t>
-  </si>
-  <si>
-    <t>spike seed surface area method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed surface area using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed surface area standard deviation</t>
-  </si>
-  <si>
-    <t>Standard deviation of Surface area</t>
-  </si>
-  <si>
-    <t>surfacearea_sd</t>
-  </si>
-  <si>
-    <t>spike seed surface area standard deviation method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed surface area standard deviation using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment.</t>
-  </si>
-  <si>
-    <t>spike seed ratio surface to volume</t>
-  </si>
-  <si>
-    <t>The ratio of surface area to seed size in volex</t>
-  </si>
-  <si>
-    <t>ratiosurfacetovolume</t>
-  </si>
-  <si>
-    <t>spike seed ratio surface to volume method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed ratio surface to volume using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>ratio</t>
-  </si>
-  <si>
-    <t>A dimensionless ratio unit which, given a pair of quantities a and b, for which b is a multiple of a, denotes b by giving the multiplier (coefficient) c for a to result in b</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0010006</t>
-  </si>
-  <si>
-    <t>spike seed mean gray value</t>
-  </si>
-  <si>
-    <t>Average gray value of the seeds on this spike, correlate to seed density. High MeanGrayValue = high seed density</t>
-  </si>
-  <si>
-    <t>meangrayvalue(hu)</t>
-  </si>
-  <si>
-    <t>spike seed mean gray value method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed mean gray value using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed mean gray value standard deviation</t>
-  </si>
-  <si>
-    <t>Standard deviation of Mean Gray Value</t>
-  </si>
-  <si>
-    <t>meangrayvalue_sd</t>
-  </si>
-  <si>
-    <t>spike seed mean gray value standard deviation method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed mean gray value standard deviation using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed ear X</t>
-  </si>
-  <si>
-    <t>Distance between the furthest apart seeds on X axis</t>
-  </si>
-  <si>
-    <t>ear_X(mm)</t>
-  </si>
-  <si>
-    <t>spike seed ear X method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed ear X using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment.</t>
-  </si>
-  <si>
-    <t>spike seed ear Y</t>
-  </si>
-  <si>
-    <t>Distance between the furthest apart seeds on Y axis</t>
-  </si>
-  <si>
-    <t>ear_Y(mm)</t>
-  </si>
-  <si>
-    <t>spike seed ear Y method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed ear Y using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed ear Z</t>
-  </si>
-  <si>
-    <t>Distance between the furthest apart seeds on Z axis</t>
-  </si>
-  <si>
-    <t>ear_Z(mm)</t>
-  </si>
-  <si>
-    <t>spike seed ear Z method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed ear Z using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment.</t>
-  </si>
-  <si>
-    <t>spike seed ear length</t>
-  </si>
-  <si>
-    <t>Longest distance between seeds base on their spatial positions</t>
-  </si>
-  <si>
-    <t>earlength(mm)</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0000431</t>
-  </si>
-  <si>
-    <t>spike seed ear length method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed ear length using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>spike seed class percentage</t>
-  </si>
-  <si>
-    <t>The percentage of grains classified as Seed Class 0, 1, 2, 3 on this spike</t>
-  </si>
-  <si>
-    <t>seedclass_0(%); seedclass_1(%); seedclass_2(%); seedclass_3(%)</t>
-  </si>
-  <si>
-    <t>spike seed class percentage method</t>
-  </si>
-  <si>
-    <t>Scanning spike seed class percentage using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
-  </si>
-  <si>
-    <t>Bettina Berger</t>
-  </si>
-  <si>
-    <t>shoot fresh weight</t>
-  </si>
-  <si>
-    <t>The total weight of shoots per plant</t>
-  </si>
-  <si>
-    <t>fresh shoot weight</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0000571</t>
-  </si>
-  <si>
-    <t>shoot fresh weight method</t>
+    <t xml:space="preserve">seedweight_avesd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed weight standard deviation method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike standard deviation of seed weight average using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed spherical ratio average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average of shape descriptor of seed on spike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sphericalratio_ave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed spherical ratio average method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike spike seed spherical ratio average using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed spherical ratio average 0-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spike seed spherical ratio average scale 0 = infinitive long cylinder shape, 1 = sphere shape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed length average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average length of seeds on this spike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedlength(mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed length average method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed length using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed length standard deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard deviation of seed length (mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedlength_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed length standard deviation method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed length standard deviation using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average seed volume in mm3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedVolume_mm3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed volume method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed volume using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Averge seed size in mm3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedsize(mm3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0000391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed size method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed size using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed size standard deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard deviation of Seed size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedsize_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed size standard deviation method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed size standard deviation using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed surface area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average seed surface area (mm2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surfacearea(mm2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed surface area method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed surface area using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed surface area standard deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard deviation of Surface area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surfacearea_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed surface area standard deviation method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed surface area standard deviation using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed ratio surface to volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ratio of surface area to seed size in volex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ratiosurfacetovolume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed ratio surface to volume method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed ratio surface to volume using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A dimensionless ratio unit which, given a pair of quantities a and b, for which b is a multiple of a, denotes b by giving the multiplier (coefficient) c for a to result in b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/UO_0010006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed mean gray value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average gray value of the seeds on this spike, correlate to seed density. High MeanGrayValue = high seed density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meangrayvalue(hu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed mean gray value method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed mean gray value using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed mean gray value standard deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard deviation of Mean Gray Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meangrayvalue_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed mean gray value standard deviation method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed mean gray value standard deviation using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed ear X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance between the furthest apart seeds on X axis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ear_X(mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed ear X method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed ear X using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed ear Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance between the furthest apart seeds on Y axis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ear_Y(mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed ear Y method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed ear Y using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed ear Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance between the furthest apart seeds on Z axis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ear_Z(mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed ear Z method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed ear Z using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed ear length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longest distance between seeds base on their spatial positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">earlength(mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0000431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed ear length method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed ear length using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed class percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The percentage of grains classified as Seed Class 0, 1, 2, 3 on this spike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seedclass_0(%); seedclass_1(%); seedclass_2(%); seedclass_3(%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spike seed class percentage method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning spike seed class percentage using an X-ray CT scanner, at 220kV voltage and 6mA current, utilizing a 0.5mm copper filter for image acquisition at a resolution of 84µm. The specimen stage rotated 220 degrees with a rotation step increment of 0.15 degrees. Throughout the 7-minute scanning duration, 1500 projections were collected at an exposure time of 250 ms each. Correction and reconstruction were carried out using the Fraunhofer EZRT CTProcessingNet, following the approach described by Schmidt et al. (2020) (DOI: 10.1186/s13007-020-00565-w). Reconstructed 3D grey-scale volume, with a depth of 16 bits, was then segmented into 30 individual 3D volumes using the EarSTubesSegmentation algorithm. Spike, automatic wheat seed segmentation and measurements were conducted using the EarS algorithm. Spikelet information, including the number of spikelets per spike and the number of grains per spikelet, estimated using a method described by Zhou et al. (2021) (DOI: 10.1186/s13007-021-00726-5), with modifications implemented in a Python 3.0 environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bettina Berger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shoot fresh weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The total weight of shoots per plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh shoot weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0000571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shoot fresh weight method</t>
   </si>
   <si>
     <t xml:space="preserve">Calculated as the total weight of the above ground plant material </t>
   </si>
   <si>
-    <t>shoot dry weight</t>
-  </si>
-  <si>
-    <t>The total weight shoots after drying</t>
-  </si>
-  <si>
-    <t>dry shoot weight</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0000552</t>
-  </si>
-  <si>
-    <t>shoot dry weight method</t>
+    <t xml:space="preserve">shoot dry weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The total weight shoots after drying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dry shoot weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0000552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shoot dry weight method</t>
   </si>
   <si>
     <t xml:space="preserve">Calculated as the total weight of the dried above ground plant material </t>
   </si>
   <si>
-    <t>root fresh weight</t>
-  </si>
-  <si>
-    <t>The total weight of roots</t>
-  </si>
-  <si>
-    <t>fresh root weight</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0000578</t>
-  </si>
-  <si>
-    <t>root fresh weight method</t>
+    <t xml:space="preserve">root fresh weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The total weight of roots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh root weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0000578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">root fresh weight method</t>
   </si>
   <si>
     <t xml:space="preserve">Calculated as the total weight of below ground plant material </t>
   </si>
   <si>
-    <t>root dry weight</t>
-  </si>
-  <si>
-    <t>The total weight of roots after drying</t>
-  </si>
-  <si>
-    <t>dry root weight</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0000078</t>
-  </si>
-  <si>
-    <t>root dry weight method</t>
+    <t xml:space="preserve">root dry weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The total weight of roots after drying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dry root weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0000078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">root dry weight method</t>
   </si>
   <si>
     <t xml:space="preserve">Calculated as the total weight of the dried below ground plant material </t>
   </si>
   <si>
-    <t>total fresh weight</t>
-  </si>
-  <si>
-    <t>The total weight of shoots and roots</t>
-  </si>
-  <si>
-    <t>total biomass</t>
-  </si>
-  <si>
-    <t>total fresh weight method</t>
+    <t xml:space="preserve">total fresh weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The total weight of shoots and roots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total biomass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total fresh weight method</t>
   </si>
   <si>
     <t xml:space="preserve">Calculated as the total weight of above and below ground plant material </t>
   </si>
   <si>
-    <t>total dry weight</t>
-  </si>
-  <si>
-    <t>The total weight of shoots and roots after drying</t>
+    <t xml:space="preserve">total dry weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The total weight of shoots and roots after drying</t>
   </si>
   <si>
     <t xml:space="preserve">total above and below ground dry weight </t>
   </si>
   <si>
-    <t>total dry weight method</t>
+    <t xml:space="preserve">total dry weight method</t>
   </si>
   <si>
     <t xml:space="preserve">Calculated as the total weight of dried above and below ground plant material </t>
   </si>
   <si>
-    <t>harvest index</t>
-  </si>
-  <si>
-    <t>Ratio of grain yield to aboveground fresh or dry biomass</t>
-  </si>
-  <si>
-    <t>ratio of total seed weight to aboveground fresh or dry weight</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/TO_0000128</t>
-  </si>
-  <si>
-    <t>harvest index method</t>
-  </si>
-  <si>
-    <t>Calculated as ratio of Yield to Biomass</t>
-  </si>
-  <si>
-    <t>gram/gram</t>
-  </si>
-  <si>
-    <t>g/g</t>
-  </si>
-  <si>
-    <t>A unit which is equal to 1 gram per 1 gram</t>
-  </si>
-  <si>
-    <t>soil nitrate concentration</t>
-  </si>
-  <si>
-    <t>Soil nitrogen concentration (mg/g) attributable to nitrate</t>
-  </si>
-  <si>
-    <t>soil NO3</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/ENVO_09200007</t>
-  </si>
-  <si>
-    <t>soil nitrate concentration method</t>
-  </si>
-  <si>
-    <t>milligram/gram</t>
+    <t xml:space="preserve">harvest index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio of grain yield to aboveground fresh or dry biomass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ratio of total seed weight to aboveground fresh or dry weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0000128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">harvest index method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculated as ratio of Yield to Biomass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gram/gram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g/g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A unit which is equal to 1 gram per 1 gram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil nitrate concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil nitrogen concentration (mg/g) attributable to nitrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil NO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/ENVO_09200007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil nitrate concentration method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">milligram/gram</t>
   </si>
   <si>
     <t xml:space="preserve">mg/g </t>
   </si>
   <si>
-    <t>A unit which is equal to 10⁻³ gram per 1 gram</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0000022; http://purl.obolibrary.org/obo/UO_0000021</t>
-  </si>
-  <si>
-    <t>soil ammonia concentration</t>
-  </si>
-  <si>
-    <t>Soil nitrogen concentration (mg/g) attributable to ammonia</t>
-  </si>
-  <si>
-    <t>soil NH4</t>
-  </si>
-  <si>
-    <t>soil ammonia concentration method</t>
-  </si>
-  <si>
-    <t>soil nitrogen concentration</t>
-  </si>
-  <si>
-    <t>The sum of the soil NO3 and NH4 concentrations (mg/g)</t>
+    <t xml:space="preserve">A unit which is equal to 10⁻³ gram per 1 gram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/UO_0000022; http://purl.obolibrary.org/obo/UO_0000021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil ammonia concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil nitrogen concentration (mg/g) attributable to ammonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil NH4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil ammonia concentration method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil nitrogen concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The sum of the soil NO3 and NH4 concentrations (mg/g)</t>
   </si>
   <si>
     <t xml:space="preserve">Total soil N concentration </t>
   </si>
   <si>
-    <t>http://purl.obolibrary.org/obo/ENVO_09000017</t>
-  </si>
-  <si>
-    <t>soil nitrogen concentration method</t>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/ENVO_09000017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil nitrogen concentration method</t>
   </si>
   <si>
     <t xml:space="preserve">projected shoot area </t>
   </si>
   <si>
-    <t>The projected shoot area of a plant</t>
-  </si>
-  <si>
-    <t>psa</t>
-  </si>
-  <si>
-    <t>projected shoot area  method</t>
-  </si>
-  <si>
-    <t>Calculated as the sum of the number of plant pixels from 3 camera views (LemnaTec Scanalyzer 3D) comprising two side views and aview from above, described by Brien et al. (2020) (https://doi.org/10.1186/s13007-020-00577-6), employing the R package growthPheno (Brien, 2021c) (http://cran.at.r-project.org/package=growthPheno)</t>
-  </si>
-  <si>
-    <t>kilopixels</t>
-  </si>
-  <si>
-    <t>kpixels</t>
-  </si>
-  <si>
-    <t>A thousand pixels quotations</t>
-  </si>
-  <si>
-    <t>absolute projected shoot area growth rates</t>
-  </si>
-  <si>
-    <t>The absolute projected shoot area growth rates (kpixels / day)</t>
-  </si>
-  <si>
-    <t>psa agr</t>
-  </si>
-  <si>
-    <t>absolute projected shoot area growth rates method</t>
-  </si>
-  <si>
-    <t>The absolute projected shoot area growth rates were calculated by differencing consecutive projected shoot area values, and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>kilopixels/day</t>
-  </si>
-  <si>
-    <t>kpixels / day</t>
-  </si>
-  <si>
-    <t>A thousand pixels quotations per day</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0000033</t>
-  </si>
-  <si>
-    <t>relative projected shoot area growth rates</t>
-  </si>
-  <si>
-    <t>The relative projected shoot area growth rates (per day)</t>
-  </si>
-  <si>
-    <t>psa rgr</t>
-  </si>
-  <si>
-    <t>relative projected shoot area growth rates method</t>
-  </si>
-  <si>
-    <t>The relative projected shoot area growth rates were calculated by differencing consecutive ln(projected shoot area) values, and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>day</t>
-  </si>
-  <si>
-    <t>A time unit which is equal to 24 hours</t>
-  </si>
-  <si>
-    <t>daily water use</t>
-  </si>
-  <si>
-    <t>The daily plant water use</t>
-  </si>
-  <si>
-    <t>wur</t>
-  </si>
-  <si>
-    <t>daily water use method</t>
-  </si>
-  <si>
-    <t>Daily water use (WUR mL/day) was computed for each pot using the Droughtspotter gravimetric platform (Droughtspotter, Phenospex, Heerlen, Netherlands) (https://phenospex.com/products/plant-phenotyping/drought-control-platform/)</t>
-  </si>
-  <si>
-    <t>milliliter/day</t>
+    <t xml:space="preserve">The projected shoot area of a plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">psa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected shoot area  method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculated as the sum of the number of plant pixels from 3 camera views (LemnaTec Scanalyzer 3D) comprising two side views and aview from above, described by Brien et al. (2020) (https://doi.org/10.1186/s13007-020-00577-6), employing the R package growthPheno (Brien, 2021c) (http://cran.at.r-project.org/package=growthPheno)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kilopixels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kpixels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A thousand pixels quotations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute projected shoot area growth rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute projected shoot area growth rates (kpixels / day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">psa agr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute projected shoot area growth rates method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute projected shoot area growth rates were calculated by differencing consecutive projected shoot area values, and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kilopixels/day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kpixels / day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A thousand pixels quotations per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/UO_0000033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative projected shoot area growth rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative projected shoot area growth rates (per day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">psa rgr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative projected shoot area growth rates method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative projected shoot area growth rates were calculated by differencing consecutive ln(projected shoot area) values, and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A time unit which is equal to 24 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daily water use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The daily plant water use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daily water use method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily water use (WUR mL/day) was computed for each pot using the Droughtspotter gravimetric platform (Droughtspotter, Phenospex, Heerlen, Netherlands) (https://phenospex.com/products/plant-phenotyping/drought-control-platform/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">milliliter/day</t>
   </si>
   <si>
     <t xml:space="preserve">ml/day </t>
   </si>
   <si>
-    <t>The total volume in milliliters used, taken, or produced over 24 hours</t>
-  </si>
-  <si>
-    <t>total water use</t>
-  </si>
-  <si>
-    <t>Defined for each plant as the sum of all daily water use values</t>
-  </si>
-  <si>
-    <t>twu</t>
-  </si>
-  <si>
-    <t>total water use method</t>
-  </si>
-  <si>
-    <t>Total Water Use (TWU) was defined for each plant as the sum of all daily WUR values (cross-reference Traits WUR - 'daily water use' [Trait ID])</t>
-  </si>
-  <si>
-    <t>milliliter</t>
-  </si>
-  <si>
-    <t>ml</t>
-  </si>
-  <si>
-    <t>A volume unit which is equal to one thousandth of a liter or 10^[-3] L, or to 1 cubic centimeter</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0000098</t>
-  </si>
-  <si>
-    <t>water use index</t>
-  </si>
-  <si>
-    <t>Water use index of the plant</t>
-  </si>
-  <si>
-    <t>wui</t>
-  </si>
-  <si>
-    <t>water use index method</t>
-  </si>
-  <si>
-    <t>Water Use Index (WUI kpixels/mL) was calculated as the ratio of smoothed projected shoot area 50 (proxy for final biomass) to TWU. Higher values of WUI correspond to higher water efficiency (cross-reference traits - smoothed projected shoot area 'smoothed Projected Shoot Area [Trait ID], TWU Total Water Use [Trait ID]), biomass [Trait ID])</t>
-  </si>
-  <si>
-    <t>kilopixels/milliliter</t>
-  </si>
-  <si>
-    <t>kpixels/ml</t>
-  </si>
-  <si>
-    <t>A thousand pixels quotations per milliliter</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0000098; http://purl.obolibrary.org/obo/UO_0000033</t>
-  </si>
-  <si>
-    <t>smoothed projected shoot area</t>
-  </si>
-  <si>
-    <t>The smoothed projected shoot area</t>
-  </si>
-  <si>
-    <t>spsa</t>
-  </si>
-  <si>
-    <t>smoothed projected shoot area method</t>
-  </si>
-  <si>
-    <t>The smoothed projected shoot area (smoothed projected shoot area kpixels) is calculated by smoothing the projected shoot area using splines as described by Brien et al. (2020) (https://doi.org/10.1186/s13007-020-00577-6), employing the R package growthPheno (Brien, 2021c) http://cran.at.r-project.org/package=growthPheno)</t>
-  </si>
-  <si>
-    <t>absolute smoothed projected shoot area growth rates</t>
-  </si>
-  <si>
-    <t>spsa agr</t>
-  </si>
-  <si>
-    <t>absolute smoothed projected shoot area growth rates method</t>
-  </si>
-  <si>
-    <t>The absolute smoothed projected shoot area growth rates were calculated by differencing consecutive smoothed projected shoot area values, respectively, and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>kpixels/day</t>
-  </si>
-  <si>
-    <t>relative smoothed projected shoot area growth rate</t>
-  </si>
-  <si>
-    <t>The relative projected shoot area growth rates (day)</t>
-  </si>
-  <si>
-    <t>spsa rgr</t>
-  </si>
-  <si>
-    <t>relative smoothed projected shoot area growth rate method</t>
-  </si>
-  <si>
-    <t>The relative smoothed projected shoot area growth rates were calculated by differencing consecutive ln(projected shoot area) values, and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>projected shoot area for a single time point</t>
-  </si>
-  <si>
-    <t>The projected shoot area for a single time point</t>
-  </si>
-  <si>
-    <t>psa for a single point</t>
-  </si>
-  <si>
-    <t>projected shoot area for a single time point method</t>
-  </si>
-  <si>
-    <t>Calculated as the sum of the number of plant pixels from 3 camera views (LemnaTec Scanalyzer 3D) comprising two side views and aview from above, described by Brien et al. (2020) (https://doi.org/10.1186/s13007-020-00577-6), employing the R package growthPheno (Brien, 2021c) http://cran.at.r-project.org/package=growthPheno)</t>
-  </si>
-  <si>
-    <t>absolute projected shoot area growth rates for a single time point</t>
-  </si>
-  <si>
-    <t>The absolute  projected shoot area growth rates for a single time point</t>
-  </si>
-  <si>
-    <t>absolute psa growth rates for a single time point</t>
-  </si>
-  <si>
-    <t>absolute projected shoot area growth rates for a single time point method</t>
-  </si>
-  <si>
-    <t>The absolute projected shoot area growth rates for a single time point were calculated by differencing consecutive projected shoot area values, and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>relative projected shoot area growth rate for a single time point</t>
-  </si>
-  <si>
-    <t>The relative projected shoot area growth rates for a single time point</t>
-  </si>
-  <si>
-    <t>relative psa growth rate for a single time point</t>
-  </si>
-  <si>
-    <t>relative projected shoot area growth rate for a single time point method</t>
-  </si>
-  <si>
-    <t>The relative projected shoot area growth rate for a single time point were calculated by differencing consecutive ln(projected shoot area) values, and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>per day</t>
-  </si>
-  <si>
-    <t>A rate, expressing the amount, frequency, or change of a quantity normalized by a time interval of one day (JCGM 200:2012; BIPM, 2019)</t>
-  </si>
-  <si>
-    <t>absolute projected shoot area growth rates over a time interval</t>
-  </si>
-  <si>
-    <t>The absolute projected shoot area growth rates over a time interval</t>
-  </si>
-  <si>
-    <t>absolute psa growth rates over a time interval</t>
-  </si>
-  <si>
-    <t>absolute projected shoot area growth rates over a time interval method</t>
-  </si>
-  <si>
-    <t>The absolute projected shoot area growth rates over a time interval were calculated by differencing projected shoot area values at two different time points, t1 and t2, and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>relative projected shoot area growth rate over a time interval</t>
-  </si>
-  <si>
-    <t>The relative projected shoot area growth rates over a time interval</t>
-  </si>
-  <si>
-    <t>relative psa growth rate over a time interval</t>
-  </si>
-  <si>
-    <t>relative projected shoot area growth rate over a time interval method</t>
-  </si>
-  <si>
-    <t>The relative projected shoot area growth rate over a time interval were calculated by differencing ln(projected shoot area) values at two different time points, t1 and t2, and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>smoothed projected shoot area for a single time point</t>
-  </si>
-  <si>
-    <t>The smoothed projected shoot area for a single time point</t>
-  </si>
-  <si>
-    <t>smoothed projected shoot area for a single time point method</t>
-  </si>
-  <si>
-    <t>The smoothed projected shoot area for a single time point is calculated by smoothing the projected shoot area using splines as described by Brien et al. (2020) (https://doi.org/10.1186/s13007-020-00577-6), employing the R package growthPheno (Brien, 2021c) (http://cran.at.r-project.org/package=growthPheno)</t>
-  </si>
-  <si>
-    <t>absolute smoothed projected shoot area growth rates for a single time point</t>
-  </si>
-  <si>
-    <t>The absolute smoothed projected shoot area growth rates for a single time point</t>
-  </si>
-  <si>
-    <t>absolute smoothed psa growth rates for a single time point</t>
-  </si>
-  <si>
-    <t>absolute smoothed projected shoot area growth rates for a single time point method</t>
-  </si>
-  <si>
-    <t>Theabsolute smoothed projected shoot area growth rates for a single time point were calculated by differencing consecutive smoothed projected shoot area values and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>relative smoothed projected shoot area growth rate for a single time point</t>
-  </si>
-  <si>
-    <t>The relative smoothed projected shoot area growth rates for a single time point</t>
-  </si>
-  <si>
-    <t>relative smoothed psa growth rate for a single time point</t>
-  </si>
-  <si>
-    <t>relative smoothed projected shoot area growth rate for a single time point method</t>
-  </si>
-  <si>
-    <t>The relative smoothed projected shoot area growth rate for a single time point were calculated by differencing consecutive ln(smoothed projected shoot area) values, and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>absolute smoothed projected shoot area growth rates over a time interval</t>
-  </si>
-  <si>
-    <t>The absolute smoothed projected shoot area growth rates over a time interval</t>
-  </si>
-  <si>
-    <t>absolute smoothed psa growth rates over a time interval</t>
-  </si>
-  <si>
-    <t>absolute smoothed projected shoot area growth rates over a time interval method</t>
-  </si>
-  <si>
-    <t>The absolute smoothed projected shoot area growth rates over a time interval were calculated by differencing smoothed projected shoot area values at two different time points, t1 and t2, and dividing by the time differences</t>
-  </si>
-  <si>
-    <t>relative smoothed projected shoot area growth rate over a time interval</t>
-  </si>
-  <si>
-    <t>The relative smoothed projected shoot area growth rates over a time interval</t>
-  </si>
-  <si>
-    <t>relative smoothed psa growth rate over a time interval</t>
-  </si>
-  <si>
-    <t>relative smoothed projected shoot area growth rate over a time interval method</t>
-  </si>
-  <si>
-    <t>The relative smoothed projected shoot area growth rate over a time interval were calculated by differencing ln(smoothed projected shoot area) values at two different time points, t1 and t2, and dividing by the time differences</t>
+    <t xml:space="preserve">The total volume in milliliters used, taken, or produced over 24 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total water use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defined for each plant as the sum of all daily water use values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">twu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total water use method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Water Use (TWU) was defined for each plant as the sum of all daily WUR values (cross-reference Traits WUR - 'daily water use' [Trait ID])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">milliliter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A volume unit which is equal to one thousandth of a liter or 10^[-3] L, or to 1 cubic centimeter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/UO_0000098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water use index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water use index of the plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water use index method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water Use Index (WUI kpixels/mL) was calculated as the ratio of smoothed projected shoot area 50 (proxy for final biomass) to TWU. Higher values of WUI correspond to higher water efficiency (cross-reference traits - smoothed projected shoot area 'smoothed Projected Shoot Area [Trait ID], TWU Total Water Use [Trait ID]), biomass [Trait ID])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kilopixels/milliliter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kpixels/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A thousand pixels quotations per milliliter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/UO_0000098; http://purl.obolibrary.org/obo/UO_0000033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoothed projected shoot area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The smoothed projected shoot area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoothed projected shoot area method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The smoothed projected shoot area (smoothed projected shoot area kpixels) is calculated by smoothing the projected shoot area using splines as described by Brien et al. (2020) (https://doi.org/10.1186/s13007-020-00577-6), employing the R package growthPheno (Brien, 2021c) http://cran.at.r-project.org/package=growthPheno)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute smoothed projected shoot area growth rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spsa agr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute smoothed projected shoot area growth rates method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute smoothed projected shoot area growth rates were calculated by differencing consecutive smoothed projected shoot area values, respectively, and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kpixels/day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative smoothed projected shoot area growth rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative projected shoot area growth rates (day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spsa rgr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative smoothed projected shoot area growth rate method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative smoothed projected shoot area growth rates were calculated by differencing consecutive ln(projected shoot area) values, and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected shoot area for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The projected shoot area for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">psa for a single point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected shoot area for a single time point method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculated as the sum of the number of plant pixels from 3 camera views (LemnaTec Scanalyzer 3D) comprising two side views and aview from above, described by Brien et al. (2020) (https://doi.org/10.1186/s13007-020-00577-6), employing the R package growthPheno (Brien, 2021c) http://cran.at.r-project.org/package=growthPheno)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute projected shoot area growth rates for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute  projected shoot area growth rates for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute psa growth rates for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute projected shoot area growth rates for a single time point method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute projected shoot area growth rates for a single time point were calculated by differencing consecutive projected shoot area values, and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative projected shoot area growth rate for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative projected shoot area growth rates for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative psa growth rate for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative projected shoot area growth rate for a single time point method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative projected shoot area growth rate for a single time point were calculated by differencing consecutive ln(projected shoot area) values, and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A rate, expressing the amount, frequency, or change of a quantity normalized by a time interval of one day (JCGM 200:2012; BIPM, 2019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute projected shoot area growth rates over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute projected shoot area growth rates over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute psa growth rates over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute projected shoot area growth rates over a time interval method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute projected shoot area growth rates over a time interval were calculated by differencing projected shoot area values at two different time points, t1 and t2, and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative projected shoot area growth rate over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative projected shoot area growth rates over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative psa growth rate over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative projected shoot area growth rate over a time interval method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative projected shoot area growth rate over a time interval were calculated by differencing ln(projected shoot area) values at two different time points, t1 and t2, and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoothed projected shoot area for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The smoothed projected shoot area for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoothed projected shoot area for a single time point method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The smoothed projected shoot area for a single time point is calculated by smoothing the projected shoot area using splines as described by Brien et al. (2020) (https://doi.org/10.1186/s13007-020-00577-6), employing the R package growthPheno (Brien, 2021c) (http://cran.at.r-project.org/package=growthPheno)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute smoothed projected shoot area growth rates for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute smoothed projected shoot area growth rates for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute smoothed psa growth rates for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute smoothed projected shoot area growth rates for a single time point method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theabsolute smoothed projected shoot area growth rates for a single time point were calculated by differencing consecutive smoothed projected shoot area values and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative smoothed projected shoot area growth rate for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative smoothed projected shoot area growth rates for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative smoothed psa growth rate for a single time point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative smoothed projected shoot area growth rate for a single time point method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative smoothed projected shoot area growth rate for a single time point were calculated by differencing consecutive ln(smoothed projected shoot area) values, and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute smoothed projected shoot area growth rates over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute smoothed projected shoot area growth rates over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute smoothed psa growth rates over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute smoothed projected shoot area growth rates over a time interval method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute smoothed projected shoot area growth rates over a time interval were calculated by differencing smoothed projected shoot area values at two different time points, t1 and t2, and dividing by the time differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative smoothed projected shoot area growth rate over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative smoothed projected shoot area growth rates over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative smoothed psa growth rate over a time interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative smoothed projected shoot area growth rate over a time interval method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The relative smoothed projected shoot area growth rate over a time interval were calculated by differencing ln(smoothed projected shoot area) values at two different time points, t1 and t2, and dividing by the time differences</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1399,7 +1398,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -1407,229 +1406,225 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="22">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+  <cellXfs count="5">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{274031F3-9333-B04B-8512-8B88EEE74CC5}"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal 2" xfId="21"/>
+    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF467886"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -1637,33 +1632,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -1676,13 +1662,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1692,15 +1672,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -1708,7 +1686,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -1716,115 +1693,91 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3462A295-73E1-634B-9FF5-D1248781B846}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:P70"/>
-  <sheetFormatPr defaultColWidth="26" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="26" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="12.125" customWidth="1"/>
-    <col min="3" max="3" width="46.625" customWidth="1"/>
-    <col min="4" max="4" width="79.5" customWidth="1"/>
-    <col min="6" max="6" width="45.625" customWidth="1"/>
-    <col min="7" max="7" width="73" customWidth="1"/>
-    <col min="8" max="8" width="38.125" customWidth="1"/>
-    <col min="9" max="9" width="70" customWidth="1"/>
-    <col min="10" max="10" width="200.125" customWidth="1"/>
-    <col min="13" max="13" width="91.125" customWidth="1"/>
-    <col min="14" max="14" width="41.625" customWidth="1"/>
-    <col min="15" max="15" width="39.875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="79.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="45.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="38.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="200.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="91.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="41.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="39.88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="0" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="1" customFormat="1">
+    <row r="2" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
@@ -1849,14 +1802,14 @@
       <c r="J2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1">
+    <row r="3" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -1878,14 +1831,14 @@
       <c r="J3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="1" customFormat="1">
+    <row r="4" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -1907,14 +1860,14 @@
       <c r="J4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="5" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -1930,8 +1883,8 @@
       <c r="E5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -1947,7 +1900,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="1" customFormat="1">
+    <row r="6" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -1963,8 +1916,8 @@
       <c r="E6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3" t="s">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1973,14 +1926,14 @@
       <c r="J6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="1" customFormat="1">
+    <row r="7" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1996,8 +1949,8 @@
       <c r="E7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -2006,14 +1959,14 @@
       <c r="J7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="1" customFormat="1">
+    <row r="8" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -2029,22 +1982,22 @@
       <c r="E8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="F8" s="4"/>
+      <c r="H8" s="4"/>
       <c r="I8" s="1" t="s">
         <v>57</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="1" customFormat="1">
+    <row r="9" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2060,9 +2013,9 @@
       <c r="E9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4" t="s">
         <v>62</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -2071,14 +2024,14 @@
       <c r="J9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="1" customFormat="1">
+    <row r="10" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -2100,14 +2053,14 @@
       <c r="J10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="1" customFormat="1">
+    <row r="11" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -2129,14 +2082,14 @@
       <c r="J11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="1" customFormat="1">
+    <row r="12" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -2158,14 +2111,14 @@
       <c r="J12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="13" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -2197,7 +2150,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="1" customFormat="1">
+    <row r="14" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -2219,14 +2172,14 @@
       <c r="J14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="15" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -2242,10 +2195,10 @@
       <c r="E15" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="3"/>
+      <c r="G15" s="4"/>
       <c r="I15" s="1" t="s">
         <v>97</v>
       </c>
@@ -2261,13 +2214,13 @@
       <c r="M15" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="N15" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+    </row>
+    <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -2283,7 +2236,7 @@
       <c r="E16" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="4" t="s">
         <v>106</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -2301,13 +2254,13 @@
       <c r="M16" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="N16" s="4" t="s">
         <v>112</v>
       </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
     </row>
-    <row r="17" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="17" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -2323,10 +2276,10 @@
       <c r="E17" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G17" s="3"/>
+      <c r="G17" s="4"/>
       <c r="I17" s="1" t="s">
         <v>116</v>
       </c>
@@ -2342,13 +2295,13 @@
       <c r="M17" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N17" s="3" t="s">
+      <c r="N17" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -2364,8 +2317,8 @@
       <c r="E18" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3" t="s">
+      <c r="F18" s="4"/>
+      <c r="G18" s="4" t="s">
         <v>121</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -2383,13 +2336,13 @@
       <c r="M18" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="N18" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
@@ -2405,10 +2358,10 @@
       <c r="E19" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G19" s="3"/>
+      <c r="G19" s="4"/>
       <c r="I19" s="1" t="s">
         <v>132</v>
       </c>
@@ -2424,11 +2377,11 @@
       <c r="M19" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
@@ -2457,7 +2410,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="21" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2486,7 +2439,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="22" spans="1:16" s="1" customFormat="1">
+    <row r="22" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2508,14 +2461,14 @@
       <c r="J22" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="M22" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="23" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>16</v>
       </c>
@@ -2531,9 +2484,9 @@
       <c r="E23" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3" t="s">
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4" t="s">
         <v>106</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -2551,13 +2504,13 @@
       <c r="M23" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="N23" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
@@ -2573,9 +2526,9 @@
       <c r="E24" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3" t="s">
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4" t="s">
         <v>106</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -2593,13 +2546,13 @@
       <c r="M24" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="N24" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
@@ -2615,9 +2568,9 @@
       <c r="E25" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3" t="s">
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4" t="s">
         <v>106</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -2635,13 +2588,13 @@
       <c r="M25" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N25" s="3" t="s">
+      <c r="N25" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
@@ -2676,7 +2629,7 @@
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
     </row>
-    <row r="27" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="27" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>16</v>
       </c>
@@ -2692,9 +2645,9 @@
       <c r="E27" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3" t="s">
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4" t="s">
         <v>96</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2712,13 +2665,13 @@
       <c r="M27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="N27" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+    </row>
+    <row r="28" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
@@ -2734,9 +2687,9 @@
       <c r="E28" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3" t="s">
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4" t="s">
         <v>96</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2754,11 +2707,11 @@
       <c r="M28" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N28" s="3" t="s">
+      <c r="N28" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="29" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
@@ -2774,7 +2727,7 @@
       <c r="E29" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="4" t="s">
         <v>131</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2793,7 +2746,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="30" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
@@ -2809,8 +2762,8 @@
       <c r="E30" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3" t="s">
+      <c r="F30" s="4"/>
+      <c r="G30" s="4" t="s">
         <v>193</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -2829,7 +2782,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:16" s="1" customFormat="1">
+    <row r="31" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>16</v>
       </c>
@@ -2845,9 +2798,9 @@
       <c r="E31" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3" t="s">
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4" t="s">
         <v>193</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -2856,14 +2809,14 @@
       <c r="J31" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="K31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="M31" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="32" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
@@ -2879,8 +2832,8 @@
       <c r="E32" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3" t="s">
+      <c r="F32" s="4"/>
+      <c r="G32" s="4" t="s">
         <v>121</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -2898,13 +2851,13 @@
       <c r="M32" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="N32" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="1:16" s="1" customFormat="1">
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+    </row>
+    <row r="33" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
@@ -2920,9 +2873,9 @@
       <c r="E33" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3" t="s">
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
         <v>121</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -2931,14 +2884,14 @@
       <c r="J33" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="K33" s="5" t="s">
+      <c r="K33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="M33" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="34" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>16</v>
       </c>
@@ -2970,7 +2923,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="35" spans="1:16" s="1" customFormat="1">
+    <row r="35" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>16</v>
       </c>
@@ -2992,14 +2945,14 @@
       <c r="J35" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="K35" s="5" t="s">
+      <c r="K35" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:16" s="1" customFormat="1">
+    <row r="36" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>16</v>
       </c>
@@ -3021,14 +2974,14 @@
       <c r="J36" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="M36" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="37" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>16</v>
       </c>
@@ -3059,13 +3012,13 @@
       <c r="M37" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N37" s="3" t="s">
+      <c r="N37" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-    </row>
-    <row r="38" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+    </row>
+    <row r="38" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>16</v>
       </c>
@@ -3096,13 +3049,13 @@
       <c r="M38" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N38" s="3" t="s">
+      <c r="N38" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
-    </row>
-    <row r="39" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+    </row>
+    <row r="39" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>16</v>
       </c>
@@ -3133,13 +3086,13 @@
       <c r="M39" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N39" s="3" t="s">
+      <c r="N39" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+    </row>
+    <row r="40" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
@@ -3155,8 +3108,8 @@
       <c r="E40" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3" t="s">
+      <c r="F40" s="4"/>
+      <c r="G40" s="4" t="s">
         <v>247</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -3174,13 +3127,13 @@
       <c r="M40" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N40" s="3" t="s">
+      <c r="N40" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="1:16" s="1" customFormat="1">
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+    </row>
+    <row r="41" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>16</v>
       </c>
@@ -3202,14 +3155,14 @@
       <c r="J41" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="K41" s="5" t="s">
+      <c r="K41" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="M41" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="42" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>16</v>
       </c>
@@ -3225,7 +3178,7 @@
       <c r="E42" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="4" t="s">
         <v>259</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -3243,13 +3196,13 @@
       <c r="M42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N42" s="3" t="s">
+      <c r="N42" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+    </row>
+    <row r="43" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>16</v>
       </c>
@@ -3265,7 +3218,7 @@
       <c r="E43" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="4" t="s">
         <v>265</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -3283,13 +3236,13 @@
       <c r="M43" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N43" s="3" t="s">
+      <c r="N43" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+    </row>
+    <row r="44" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>16</v>
       </c>
@@ -3305,7 +3258,7 @@
       <c r="E44" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="4" t="s">
         <v>271</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -3323,13 +3276,13 @@
       <c r="M44" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N44" s="3" t="s">
+      <c r="N44" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+    </row>
+    <row r="45" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>16</v>
       </c>
@@ -3345,7 +3298,7 @@
       <c r="E45" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="4" t="s">
         <v>277</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -3363,13 +3316,13 @@
       <c r="M45" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N45" s="3" t="s">
+      <c r="N45" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+    </row>
+    <row r="46" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>16</v>
       </c>
@@ -3400,13 +3353,13 @@
       <c r="M46" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N46" s="3" t="s">
+      <c r="N46" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+    </row>
+    <row r="47" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>16</v>
       </c>
@@ -3437,13 +3390,13 @@
       <c r="M47" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N47" s="3" t="s">
+      <c r="N47" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+    </row>
+    <row r="48" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>16</v>
       </c>
@@ -3459,10 +3412,10 @@
       <c r="E48" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G48" s="3"/>
+      <c r="G48" s="4"/>
       <c r="I48" s="1" t="s">
         <v>294</v>
       </c>
@@ -3478,11 +3431,11 @@
       <c r="M48" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="O48" s="3" t="s">
+      <c r="O48" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="49" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>16</v>
       </c>
@@ -3498,10 +3451,10 @@
       <c r="E49" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="G49" s="3"/>
+      <c r="G49" s="4"/>
       <c r="I49" s="1" t="s">
         <v>303</v>
       </c>
@@ -3514,11 +3467,11 @@
       <c r="M49" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="O49" s="3" t="s">
+      <c r="O49" s="4" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="50" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="50" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>16</v>
       </c>
@@ -3546,11 +3499,11 @@
       <c r="M50" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="O50" s="3" t="s">
+      <c r="O50" s="4" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="51" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="51" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>16</v>
       </c>
@@ -3566,10 +3519,10 @@
       <c r="E51" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="G51" s="3"/>
+      <c r="G51" s="4"/>
       <c r="I51" s="1" t="s">
         <v>316</v>
       </c>
@@ -3582,11 +3535,11 @@
       <c r="M51" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="O51" s="3" t="s">
+      <c r="O51" s="4" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="52" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="52" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
         <v>16</v>
       </c>
@@ -3618,7 +3571,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="53" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="53" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
         <v>16</v>
       </c>
@@ -3649,11 +3602,11 @@
       <c r="M53" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="P53" s="3" t="s">
+      <c r="P53" s="4" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="54" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>16</v>
       </c>
@@ -3681,13 +3634,13 @@
       <c r="M54" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="N54" s="3" t="s">
+      <c r="N54" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+    </row>
+    <row r="55" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
         <v>16</v>
       </c>
@@ -3719,7 +3672,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="56" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>16</v>
       </c>
@@ -3750,13 +3703,13 @@
       <c r="M56" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="N56" s="3" t="s">
+      <c r="N56" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="O56" s="3"/>
-      <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+    </row>
+    <row r="57" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>16</v>
       </c>
@@ -3787,11 +3740,11 @@
       <c r="M57" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="P57" s="3" t="s">
+      <c r="P57" s="4" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="58" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="58" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>16</v>
       </c>
@@ -3823,7 +3776,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="59" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="59" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>16</v>
       </c>
@@ -3854,11 +3807,11 @@
       <c r="M59" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="P59" s="3" t="s">
+      <c r="P59" s="4" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="60" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="60" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>16</v>
       </c>
@@ -3886,13 +3839,13 @@
       <c r="M60" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="N60" s="3" t="s">
+      <c r="N60" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+    </row>
+    <row r="61" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>16</v>
       </c>
@@ -3924,7 +3877,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="62" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="62" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>16</v>
       </c>
@@ -3955,11 +3908,11 @@
       <c r="M62" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="P62" s="3" t="s">
+      <c r="P62" s="4" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="63" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="63" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>16</v>
       </c>
@@ -3987,12 +3940,12 @@
       <c r="M63" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="O63" s="3" t="s">
+      <c r="O63" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="P63" s="4"/>
+    </row>
+    <row r="64" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>16</v>
       </c>
@@ -4024,7 +3977,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="65" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="65" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>16</v>
       </c>
@@ -4052,12 +4005,12 @@
       <c r="M65" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="O65" s="3" t="s">
+      <c r="O65" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="P65" s="4"/>
+    </row>
+    <row r="66" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>16</v>
       </c>
@@ -4089,7 +4042,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="67" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="67" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>16</v>
       </c>
@@ -4121,7 +4074,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="68" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>16</v>
       </c>
@@ -4149,12 +4102,12 @@
       <c r="M68" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="O68" s="3" t="s">
+      <c r="O68" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="1:16" s="1" customFormat="1" ht="15">
+      <c r="P68" s="4"/>
+    </row>
+    <row r="69" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>16</v>
       </c>
@@ -4186,7 +4139,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="70" spans="1:16" s="1" customFormat="1" ht="15">
+    <row r="70" s="1" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
         <v>16</v>
       </c>
@@ -4214,76 +4167,83 @@
       <c r="M70" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="O70" s="3" t="s">
+      <c r="O70" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="P70" s="3"/>
+      <c r="P70" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N15" r:id="rId1" xr:uid="{3ED55D00-C312-FE4C-B541-99EDA49E01DE}"/>
-    <hyperlink ref="N17" r:id="rId2" xr:uid="{78253DAD-FEC6-7245-B4BD-3C168E3C7615}"/>
-    <hyperlink ref="N18" r:id="rId3" xr:uid="{991ABAE0-F1C3-F148-90E5-C6AABF48FAEA}"/>
-    <hyperlink ref="N23" r:id="rId4" xr:uid="{CE946951-A5AD-7148-8039-33F6D7FF347D}"/>
-    <hyperlink ref="N24" r:id="rId5" xr:uid="{8175D832-E6FA-0F4E-8118-C901AC10C36F}"/>
-    <hyperlink ref="N25" r:id="rId6" xr:uid="{E91B3C7F-2985-3441-885C-A382E51D9AE1}"/>
-    <hyperlink ref="N27" r:id="rId7" xr:uid="{2F9586D9-285E-9C45-9F34-3586D3870C51}"/>
-    <hyperlink ref="N32" r:id="rId8" xr:uid="{B4D65294-192F-BB4A-A6B1-2480F15D6CF7}"/>
-    <hyperlink ref="N37" r:id="rId9" xr:uid="{742C5369-851B-2D47-B804-9287F131F617}"/>
-    <hyperlink ref="N38" r:id="rId10" xr:uid="{F2566086-1863-F448-891C-3FC66283CF32}"/>
-    <hyperlink ref="N39" r:id="rId11" xr:uid="{D8151173-EBDC-F34F-AC84-08DFAD2C3312}"/>
-    <hyperlink ref="N40" r:id="rId12" xr:uid="{5ECC6B44-614C-BC4A-824F-ED9C424769F6}"/>
-    <hyperlink ref="N42" r:id="rId13" xr:uid="{B7C90D35-3E0E-9548-A03A-138B355CA6CF}"/>
-    <hyperlink ref="N43" r:id="rId14" xr:uid="{A85084C3-C622-0649-8985-147B8469071F}"/>
-    <hyperlink ref="N44" r:id="rId15" xr:uid="{618A4914-94B8-7047-8A3A-8119B94A4D64}"/>
-    <hyperlink ref="N45" r:id="rId16" xr:uid="{374288EF-94BF-E541-880D-E0950ED0BC5B}"/>
-    <hyperlink ref="N46" r:id="rId17" xr:uid="{C3BC0201-A0FF-DF40-821E-443F7EA9548A}"/>
-    <hyperlink ref="N47" r:id="rId18" xr:uid="{5125DEA1-8775-7742-B842-DB51DDE7514F}"/>
-    <hyperlink ref="N54" r:id="rId19" xr:uid="{86716511-DE4B-D540-87B7-A831E035CEBF}"/>
-    <hyperlink ref="N60" r:id="rId20" xr:uid="{634863AB-5D4F-114B-87FD-4ACBE6A223EF}"/>
-    <hyperlink ref="O63" r:id="rId21" xr:uid="{B574DD33-2BFF-9545-833F-2B5A193185F7}"/>
-    <hyperlink ref="O65" r:id="rId22" xr:uid="{DF4AD675-CDA5-1C4C-9855-9A07FE995944}"/>
-    <hyperlink ref="O68" r:id="rId23" xr:uid="{6EF48A4C-9A20-DC4A-B79B-CFC43F47C32D}"/>
-    <hyperlink ref="O70" r:id="rId24" xr:uid="{04A92EE0-C228-8F4A-B2BF-9601D6C5042B}"/>
-    <hyperlink ref="N56" r:id="rId25" xr:uid="{E95939E5-DE71-BE41-8725-10A3B770F26D}"/>
-    <hyperlink ref="G5" r:id="rId26" xr:uid="{6E304CB5-7D28-CF4F-9337-B8A6795E9476}"/>
-    <hyperlink ref="G6" r:id="rId27" xr:uid="{C8F2BEB7-96B1-1D4E-B349-073E2EB74696}"/>
-    <hyperlink ref="G7" r:id="rId28" xr:uid="{EF3749DC-0D7D-EE44-8569-E3C27CCCE7D2}"/>
-    <hyperlink ref="H9" r:id="rId29" xr:uid="{537C7750-0FDB-9246-9DE0-2CF3E34437D8}"/>
-    <hyperlink ref="F17" r:id="rId30" xr:uid="{F202221B-FB0D-F444-9DE9-20B8850BAEFE}"/>
-    <hyperlink ref="G18" r:id="rId31" xr:uid="{24B507BF-7DDB-F445-B5B8-BE4D84BF818C}"/>
-    <hyperlink ref="F19" r:id="rId32" xr:uid="{556F6BD5-7AC7-8C4C-B10C-22F80A83F09B}"/>
-    <hyperlink ref="H23" r:id="rId33" xr:uid="{6EFB9CC9-E0BD-0949-8E9D-901ECF29EE07}"/>
-    <hyperlink ref="H24" r:id="rId34" xr:uid="{CB9FFBE7-19A8-3D48-BED0-B64B0B709A2C}"/>
-    <hyperlink ref="H25" r:id="rId35" xr:uid="{85CD9DAA-298B-FD44-9D13-2D3C3B23EC6B}"/>
-    <hyperlink ref="H27" r:id="rId36" xr:uid="{D7B35277-1D74-AF4E-8B0F-6C4C03B17CC4}"/>
-    <hyperlink ref="H28" r:id="rId37" xr:uid="{4F442FC6-FF48-0E4E-A930-EA8B7F16A926}"/>
-    <hyperlink ref="G30" r:id="rId38" xr:uid="{7FA11E3B-7026-1D48-8282-BDA04418AAA9}"/>
-    <hyperlink ref="H31" r:id="rId39" xr:uid="{17413E21-8E0F-4843-BC4F-6D0C03356286}"/>
-    <hyperlink ref="G32" r:id="rId40" xr:uid="{C4BB7EFB-2793-CF4E-AA69-9AF4654C5432}"/>
-    <hyperlink ref="H33" r:id="rId41" xr:uid="{A93B0A3C-33BF-294E-92EB-C5C77FEE99FE}"/>
-    <hyperlink ref="G40" r:id="rId42" xr:uid="{3CF9291F-FB5E-FE46-BAB8-921F0784B635}"/>
-    <hyperlink ref="F42" r:id="rId43" xr:uid="{E5FE7B47-CD63-4543-9AEA-0BC94A5E6FEF}"/>
-    <hyperlink ref="F43" r:id="rId44" xr:uid="{90404AF5-03C4-9446-8D53-597D170503AF}"/>
-    <hyperlink ref="F44" r:id="rId45" xr:uid="{6A8FBAB6-B079-D043-845D-880108DF6C9E}"/>
-    <hyperlink ref="F45" r:id="rId46" xr:uid="{EEB7F217-FFC0-DC41-9367-FB4DD57DE878}"/>
-    <hyperlink ref="F48" r:id="rId47" xr:uid="{5EC371B7-0BF9-0C4A-8F9B-8E6CC6C6A149}"/>
-    <hyperlink ref="F49" r:id="rId48" xr:uid="{9796E10B-F2F2-FA41-B86A-38DFFB9AA958}"/>
-    <hyperlink ref="F51" r:id="rId49" xr:uid="{6715528F-882C-2840-884E-15F81B1FE757}"/>
-    <hyperlink ref="F15" r:id="rId50" xr:uid="{AF945093-5D81-D943-B643-344023E1BD32}"/>
-    <hyperlink ref="O48" r:id="rId51" xr:uid="{EFF22231-276F-8447-A547-4A22B3FE6C81}"/>
-    <hyperlink ref="O49" r:id="rId52" display="http://purl.obolibrary.org/obo/UO_0000021" xr:uid="{151486AD-2E30-1B4E-BADB-5D777B58DD4F}"/>
-    <hyperlink ref="O50:O51" r:id="rId53" display="http://purl.obolibrary.org/obo/UO_0000021" xr:uid="{9E2628BB-BFE3-AC46-8F22-3FE62BEA5C9B}"/>
-    <hyperlink ref="P57" r:id="rId54" display="http://purl.obolibrary.org/obo/UO_0000016" xr:uid="{06FB953B-E0EC-1840-ACF8-D6050E681F40}"/>
-    <hyperlink ref="P53" r:id="rId55" xr:uid="{16FF44B8-BAB4-954D-9BA4-F6450A810801}"/>
-    <hyperlink ref="P59" r:id="rId56" xr:uid="{C63814E0-1614-0A48-82BC-BC12DF07835A}"/>
-    <hyperlink ref="P62" r:id="rId57" xr:uid="{D7586F63-5ECD-A248-B41D-982D263AE52C}"/>
-    <hyperlink ref="N16" r:id="rId58" xr:uid="{55EABB47-ECE0-CF48-B117-047B224FE0CD}"/>
-    <hyperlink ref="F29" r:id="rId59" xr:uid="{8A3C27DD-E1A8-4F49-933C-68F4FC9C1C4D}"/>
-    <hyperlink ref="G16" r:id="rId60" xr:uid="{A3E9B132-E2D0-8A4E-881B-9C709E3E19A9}"/>
-    <hyperlink ref="N28" r:id="rId61" xr:uid="{4D1F452B-BC11-DB46-8CE7-1BEBF5C3EF49}"/>
+    <hyperlink ref="G5" r:id="rId1" display="http://purl.obolibrary.org/obo/FLOPO_0002293"/>
+    <hyperlink ref="G6" r:id="rId2" display="http://purl.obolibrary.org/obo/FLOPO_0002293"/>
+    <hyperlink ref="G7" r:id="rId3" display="http://purl.obolibrary.org/obo/FLOPO_0002293"/>
+    <hyperlink ref="H9" r:id="rId4" display="http://purl.obolibrary.org/obo/FLOPO_0015519"/>
+    <hyperlink ref="F15" r:id="rId5" display="http://purl.obolibrary.org/obo/TO_0000146"/>
+    <hyperlink ref="N15" r:id="rId6" display="http://purl.obolibrary.org/obo/UO_0000016"/>
+    <hyperlink ref="G16" r:id="rId7" display="http://purl.obolibrary.org/obo/TO_0000181"/>
+    <hyperlink ref="N16" r:id="rId8" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="F17" r:id="rId9" display="http://purl.obolibrary.org/obo/TO_0000181"/>
+    <hyperlink ref="N17" r:id="rId10" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="G18" r:id="rId11" display="http://purl.obolibrary.org/obo/TO_0002741"/>
+    <hyperlink ref="N18" r:id="rId12" display="http://purl.obolibrary.org/obo/UO_0000082"/>
+    <hyperlink ref="F19" r:id="rId13" display="http://purl.obolibrary.org/obo/TO_0007000"/>
+    <hyperlink ref="H23" r:id="rId14" display="http://purl.obolibrary.org/obo/TO_0000181"/>
+    <hyperlink ref="N23" r:id="rId15" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="H24" r:id="rId16" display="http://purl.obolibrary.org/obo/TO_0000181"/>
+    <hyperlink ref="N24" r:id="rId17" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="H25" r:id="rId18" display="http://purl.obolibrary.org/obo/TO_0000181"/>
+    <hyperlink ref="N25" r:id="rId19" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="H27" r:id="rId20" display="http://purl.obolibrary.org/obo/TO_0000146"/>
+    <hyperlink ref="N27" r:id="rId21" display="http://purl.obolibrary.org/obo/UO_0000016"/>
+    <hyperlink ref="H28" r:id="rId22" display="http://purl.obolibrary.org/obo/TO_0000146"/>
+    <hyperlink ref="N28" r:id="rId23" display="http://purl.obolibrary.org/obo/UO_0000016"/>
+    <hyperlink ref="F29" r:id="rId24" display="http://purl.obolibrary.org/obo/TO_0007000"/>
+    <hyperlink ref="G30" r:id="rId25" display="http://purl.obolibrary.org/obo/TO_0000391"/>
+    <hyperlink ref="H31" r:id="rId26" display="http://purl.obolibrary.org/obo/TO_0000391"/>
+    <hyperlink ref="G32" r:id="rId27" display="http://purl.obolibrary.org/obo/TO_0002741"/>
+    <hyperlink ref="N32" r:id="rId28" display="http://purl.obolibrary.org/obo/UO_0000082"/>
+    <hyperlink ref="H33" r:id="rId29" display="http://purl.obolibrary.org/obo/TO_0002741"/>
+    <hyperlink ref="N37" r:id="rId30" display="http://purl.obolibrary.org/obo/UO_0000016"/>
+    <hyperlink ref="N38" r:id="rId31" display="http://purl.obolibrary.org/obo/UO_0000016"/>
+    <hyperlink ref="N39" r:id="rId32" display="http://purl.obolibrary.org/obo/UO_0000016"/>
+    <hyperlink ref="G40" r:id="rId33" display="http://purl.obolibrary.org/obo/TO_0000431"/>
+    <hyperlink ref="N40" r:id="rId34" display="http://purl.obolibrary.org/obo/UO_0000016"/>
+    <hyperlink ref="F42" r:id="rId35" display="http://purl.obolibrary.org/obo/TO_0000571"/>
+    <hyperlink ref="N42" r:id="rId36" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="F43" r:id="rId37" display="http://purl.obolibrary.org/obo/TO_0000552"/>
+    <hyperlink ref="N43" r:id="rId38" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="F44" r:id="rId39" display="http://purl.obolibrary.org/obo/TO_0000578"/>
+    <hyperlink ref="N44" r:id="rId40" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="F45" r:id="rId41" display="http://purl.obolibrary.org/obo/TO_0000078"/>
+    <hyperlink ref="N45" r:id="rId42" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="N46" r:id="rId43" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="N47" r:id="rId44" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="F48" r:id="rId45" display="http://purl.obolibrary.org/obo/TO_0000128"/>
+    <hyperlink ref="O48" r:id="rId46" display="http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="F49" r:id="rId47" display="http://purl.obolibrary.org/obo/ENVO_09200007"/>
+    <hyperlink ref="O49" r:id="rId48" display="http://purl.obolibrary.org/obo/UO_0000022; http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="O50" r:id="rId49" display="http://purl.obolibrary.org/obo/UO_0000022; http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="F51" r:id="rId50" display="http://purl.obolibrary.org/obo/ENVO_09000017"/>
+    <hyperlink ref="O51" r:id="rId51" display="http://purl.obolibrary.org/obo/UO_0000022; http://purl.obolibrary.org/obo/UO_0000021"/>
+    <hyperlink ref="P53" r:id="rId52" display="http://purl.obolibrary.org/obo/UO_0000033"/>
+    <hyperlink ref="N54" r:id="rId53" display="http://purl.obolibrary.org/obo/UO_0000033"/>
+    <hyperlink ref="N56" r:id="rId54" display="http://purl.obolibrary.org/obo/UO_0000098"/>
+    <hyperlink ref="P57" r:id="rId55" display="http://purl.obolibrary.org/obo/UO_0000098; http://purl.obolibrary.org/obo/UO_0000033"/>
+    <hyperlink ref="P59" r:id="rId56" display="http://purl.obolibrary.org/obo/UO_0000033"/>
+    <hyperlink ref="N60" r:id="rId57" display="http://purl.obolibrary.org/obo/UO_0000033"/>
+    <hyperlink ref="P62" r:id="rId58" display="http://purl.obolibrary.org/obo/UO_0000033"/>
+    <hyperlink ref="O63" r:id="rId59" display="http://purl.obolibrary.org/obo/UO_0000033"/>
+    <hyperlink ref="O65" r:id="rId60" display="http://purl.obolibrary.org/obo/UO_0000033"/>
+    <hyperlink ref="O68" r:id="rId61" display="http://purl.obolibrary.org/obo/UO_0000033"/>
+    <hyperlink ref="O70" r:id="rId62" display="http://purl.obolibrary.org/obo/UO_0000033"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
